--- a/old/260726.xlsx
+++ b/old/260726.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD14545-77F1-412F-99A7-E7AA04B4ED30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B7D1B6-9D9F-4EDB-9908-7B567593B472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8400" yWindow="4110" windowWidth="15030" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10500" yWindow="4110" windowWidth="15010" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>每周采访-160731-Generalbundesanwalt</t>
   </si>
@@ -639,21 +639,6 @@
 Und nur, wenn wir diesen Rechtsrahmen auch konsequent verteidigen – und dazu gehört eine konsequente Strafverfolgung – nur, wenn wir diesen Rechtsrahmen verteidigen, dann haben wir eine Chance, dass das Recht und damit auch die Werte erhalten bleiben.
 Geuther: Herr Generalbundesanwalt, vielen Dank für das Gespräch.</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>auch in den Wahlkampf ziehen will</t>
-  </si>
-  <si>
-    <t>Ich bin übrigens auch nicht dafür</t>
-  </si>
-  <si>
-    <t>besser als bei uns</t>
-  </si>
-  <si>
-    <t>Sanierungsstau</t>
-  </si>
-  <si>
-    <t>Unbotmäßiges</t>
   </si>
   <si>
     <t>Deswegen müssen wir</t>
@@ -990,40 +975,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58E0FF61-1578-4139-819D-7DBEAF65C891}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1064,14 +1024,14 @@
     <col min="1" max="1" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
